--- a/deliverables/qc_gap_analysis/tracker/CoQ_references_v41.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/CoQ_references_v41.xlsx
@@ -1138,7 +1138,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>ППК25139 —; 627/1128/25 24.06.25; 3176/2025 23.06.25</t>
+          <t>ППК25139 —; 471-0862-25 16.05.25; 2471-2025 15.05.25</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1183,22 +1183,22 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>627/1128/25 02.07.25 IJZ-MB</t>
+          <t>471-0862-25 22.05.25 IJZ-MB</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>3176/2025 26.06.25 IJZ; also 197-11-М/26; n/t 10.1,10.3</t>
+          <t>2471-2025 30.05.25 IJZ; also 197-11-М/26; n/t 10.1,10.3</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>3176/2025 26.06.25 IJZ</t>
+          <t>2471-2025 30.05.25 IJZ</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3176/2025 26.06.25 IJZ</t>
+          <t>2471-2025 30.05.25 IJZ</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>ППК25117 28.04.25; 2156/2025 28.04.25</t>
+          <t>ППК25117 28.04.25; 407-0745-25 29.04.25; 2156/2025 28.04.25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2156/2025 07.05.25 IJZ</t>
+          <t>407-0745-25 05.05.25 IJZ-MB</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>534/1065/26 31.08.26 IJZ</t>
+          <t>534/1065/26 31.08.26 IJZ-MB</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -10659,7 +10659,7 @@
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>535/1066/26 31.08.26 IJZ</t>
+          <t>535/1066/26 31.08.26 IJZ-MB</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
@@ -16913,7 +16913,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>3176/2025 26.06.25 IJZ; also 197-11-М/26; n/t 10.1,10.3</t>
+          <t>2471-2025 30.05.25 IJZ; also 197-11-М/26; n/t 10.1,10.3</t>
         </is>
       </c>
     </row>
